--- a/static/example_sheets_online/eDNA robot sampling.xlsx
+++ b/static/example_sheets_online/eDNA robot sampling.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A9B927-DA6B-4316-8FF6-3DAA506B463D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34F890D-9723-4639-8F33-DE215C9F2D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{C398C9AD-1A63-418B-90C4-5868F530D2EC}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">eDNA_Subsampling_for_robot_pipe!$B$1:$M$6</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">eDNA_Subsampling_for_robot_pipe!$B$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>Rack161</t>
   </si>
@@ -56,24 +56,9 @@
     <t>Tjørnin pilot study</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>text and/or numbers</t>
-  </si>
-  <si>
-    <t>number (decimals allowed)</t>
-  </si>
-  <si>
     <t>Expected column names and positions:</t>
   </si>
   <si>
-    <t>Expected data type:</t>
-  </si>
-  <si>
     <t>Example of accepted data:</t>
   </si>
   <si>
@@ -116,9 +101,6 @@
     <t>RemarksSubmission</t>
   </si>
   <si>
-    <t>date or free text</t>
-  </si>
-  <si>
     <t>LV7005368197</t>
   </si>
   <si>
@@ -147,12 +129,6 @@
   </si>
   <si>
     <t>Accepted format:</t>
-  </si>
-  <si>
-    <t>Required column*</t>
-  </si>
-  <si>
-    <t>*If a column is required, this means that the sheet will be rejected if there are any values missing from that column</t>
   </si>
   <si>
     <t>YYYY-MM-DD or DD-MM-YYYY</t>
@@ -194,15 +170,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -293,30 +266,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{122CF2A6-8044-42EF-B290-7B8E197B9F21}" name="eDNA_Subsampling_for_robot_pipeline_230927_KHK_ISL_Tjørnen_Pilot_ds_test" displayName="eDNA_Subsampling_for_robot_pipeline_230927_KHK_ISL_Tjørnen_Pilot_ds_test" ref="B1:M6" tableType="queryTable" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="B1:M6" xr:uid="{122CF2A6-8044-42EF-B290-7B8E197B9F21}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{122CF2A6-8044-42EF-B290-7B8E197B9F21}" name="eDNA_Subsampling_for_robot_pipeline_230927_KHK_ISL_Tjørnen_Pilot_ds_test" displayName="eDNA_Subsampling_for_robot_pipeline_230927_KHK_ISL_Tjørnen_Pilot_ds_test" ref="B1:M4" tableType="queryTable" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="B1:M4" xr:uid="{122CF2A6-8044-42EF-B290-7B8E197B9F21}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{61CE2CF1-CB87-4D93-96B1-F79B80037F8B}" uniqueName="1" name="SubSampleID" queryTableFieldId="1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1225E0D6-85DB-445F-A353-E6838F05309F}" uniqueName="2" name="RackName" queryTableFieldId="2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{80EE4D20-DB5C-4C41-8E7C-CFA1A54D0D6F}" uniqueName="3" name="RackID" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{E63ABEC4-D6D9-42F6-8517-6BA1D2DAD6D0}" uniqueName="4" name="PositionInRack" queryTableFieldId="4" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{06FD67DC-9E4F-421F-B4C6-499BC81489AD}" uniqueName="5" name="Mass" queryTableFieldId="5" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{6BFE5EDA-F033-4EDE-BFF6-8AB49D501C7E}" uniqueName="6" name="SampledBy" queryTableFieldId="6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{90C5282A-2E48-49FB-AD72-B417D2D78019}" uniqueName="7" name="SamplingDate" queryTableFieldId="7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{D6A83E12-FDA9-4E95-8F5E-592335C9E9BC}" uniqueName="8" name="RemarksSubSampling" queryTableFieldId="8" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{577832FC-2075-46B4-8BE0-4D958440D904}" uniqueName="9" name="ArchiveSampleID" queryTableFieldId="9" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{9350DA4F-6164-4C19-8529-CC72D7444991}" uniqueName="10" name="Submitter" queryTableFieldId="10" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{4E6278EE-5B6B-47F3-A8C0-E7F7EF542A93}" uniqueName="11" name="SubmissionDate" queryTableFieldId="11" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{5E24FE6E-838B-4B5F-A7B0-81F0EDBECB32}" uniqueName="12" name="RemarksSubmission" queryTableFieldId="12" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{61CE2CF1-CB87-4D93-96B1-F79B80037F8B}" uniqueName="1" name="SubSampleID" queryTableFieldId="1" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{1225E0D6-85DB-445F-A353-E6838F05309F}" uniqueName="2" name="RackName" queryTableFieldId="2" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{80EE4D20-DB5C-4C41-8E7C-CFA1A54D0D6F}" uniqueName="3" name="RackID" queryTableFieldId="3" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{E63ABEC4-D6D9-42F6-8517-6BA1D2DAD6D0}" uniqueName="4" name="PositionInRack" queryTableFieldId="4" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{06FD67DC-9E4F-421F-B4C6-499BC81489AD}" uniqueName="5" name="Mass" queryTableFieldId="5" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{6BFE5EDA-F033-4EDE-BFF6-8AB49D501C7E}" uniqueName="6" name="SampledBy" queryTableFieldId="6" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{90C5282A-2E48-49FB-AD72-B417D2D78019}" uniqueName="7" name="SamplingDate" queryTableFieldId="7" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{D6A83E12-FDA9-4E95-8F5E-592335C9E9BC}" uniqueName="8" name="RemarksSubSampling" queryTableFieldId="8" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{577832FC-2075-46B4-8BE0-4D958440D904}" uniqueName="9" name="ArchiveSampleID" queryTableFieldId="9" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{9350DA4F-6164-4C19-8529-CC72D7444991}" uniqueName="10" name="Submitter" queryTableFieldId="10" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{4E6278EE-5B6B-47F3-A8C0-E7F7EF542A93}" uniqueName="11" name="SubmissionDate" queryTableFieldId="11" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{5E24FE6E-838B-4B5F-A7B0-81F0EDBECB32}" uniqueName="12" name="RemarksSubmission" queryTableFieldId="12" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -354,7 +327,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -460,7 +433,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,7 +575,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -610,202 +583,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB558DD9-22B2-4103-9EAD-3D84A5EB9314}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33" style="1" customWidth="1"/>
-    <col min="2" max="5" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="5" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" t="s">
         <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>111</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>4</v>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1">
-        <v>111</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>1</v>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>34</v>
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/static/example_sheets_online/eDNA robot sampling.xlsx
+++ b/static/example_sheets_online/eDNA robot sampling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34F890D-9723-4639-8F33-DE215C9F2D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969868B9-A92B-4810-86D0-8EC7EEA67A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{C398C9AD-1A63-418B-90C4-5868F530D2EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{C398C9AD-1A63-418B-90C4-5868F530D2EC}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Subsampling_for_robot_pipe" sheetId="2" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Example of accepted data:</t>
   </si>
   <si>
-    <t>gko001</t>
-  </si>
-  <si>
     <t>SubSampleID</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>2023-06-11</t>
   </si>
   <si>
-    <t xml:space="preserve">jkl123; lpk234	</t>
-  </si>
-  <si>
     <t>negative control</t>
   </si>
   <si>
@@ -131,10 +125,16 @@
     <t>Accepted format:</t>
   </si>
   <si>
-    <t>YYYY-MM-DD or DD-MM-YYYY</t>
-  </si>
-  <si>
-    <t>KU-ID, seperated by semicolon if multiple</t>
+    <t xml:space="preserve">Jens Jensen; Peter Petersen	</t>
+  </si>
+  <si>
+    <t>See 'Person Identifiers' in manual.</t>
+  </si>
+  <si>
+    <t>Ole Olsen</t>
+  </si>
+  <si>
+    <t>See options on the website</t>
   </si>
 </sst>
 </file>
@@ -603,40 +603,40 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -644,37 +644,37 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>111</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="M2" t="s">
         <v>1</v>
@@ -682,24 +682,24 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
